--- a/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-correction.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-09-persistent-matmul-correction.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -46,7 +46,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课节点 1–2 的检查题：块 128 × 128 × 64、M = N = 8192，持久化相对逐 tile 发射的收益在哪里。</t>
+          <t xml:space="preserve">块 128 × 128 × 64、M = N = 8192 的矩阵乘：比较持久化相对逐 tile 发射的收益在哪里。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -71,12 +71,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">判断 Triton kernel 把 num_stages 加大、共享内存超过设备上限时会发生什么。</t>
+          <t xml:space="preserve">判断在 Triton 3.7.1 中，kernel 把 num_stages 加大、共享内存超过设备上限时会发生什么。</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课节点 3：flatten 版持久化矩阵乘多加一级流水后，共享内存需要 131,072 字节，超过设备上限。</t>
+          <t xml:space="preserve">flatten 版持久化矩阵乘多加一级流水后，共享内存需要 131,072 字节，超过了设备每个 CTA 的上限。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -106,7 +106,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课节点 4：块 128 × 128 × 64、fp16 的矩阵乘在两代 GPU 上的共享内存用量不同。</t>
+          <t xml:space="preserve">块 128 × 128 × 64、fp16 的矩阵乘：sm_90 比 sm_89 多用共享内存、少用寄存器。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -124,6 +124,7 @@
           <t xml:space="preserve">[T#B,!36b59d#结论]：输入槽数由 num_stages 和乘加指令能否直接从共享内存读操作数共同决定，与指令一条算多大、用不用 TMA 都无关。
 • [T#B#sm_89]：ldmatrix 把操作数取进寄存器后，这个槽就能装下一轮的数据，同时在路上的轮数为 S − 1。
 • [T#B#sm_90]：wgmma 发出后还在读共享内存，等它完成槽才能复用，于是要再多一个槽。
+• [T#B#提前量]：两代的提前量相同，都是 S − 1 轮。把 sm_90 共享内存变多说成“为了让更多数据提前搬”也是误解：多出的是被就地读的操作数占着的槽，sm_90 寄存器少，正因为操作数不进寄存器。
 [T#B,!c47f17#边界]：sm_120 的乘加仍是 mma.sync，即使用 TMA 搬入，也只要 S − 1 个槽。</t>
         </is>
       </c>
@@ -136,7 +137,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课节点 5–6：比较 warp 专用化之后，搬运分区为什么不在 tile 边界停顿。</t>
+          <t xml:space="preserve">对照：warp 专用化之后，搬运分区不会在 tile 边界停顿。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -161,12 +162,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">找出分块矩阵乘里 K 不是块的整数倍时结果出错的原因：K 方向先用 tl.where 把越界下标改成 0，再用改写后的下标算 mask。</t>
+          <t xml:space="preserve">找出这段 K 方向越界处理的错误，并说明 M = N = K = 1 时输出 96 是怎么来的。</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课练习的首版：失败的形状全是 K 不是 block_k 整数倍的；M = N = K = 1、a = 2、b = 3、block_k = 16 时输出 96。</t>
+          <t xml:space="preserve">分块矩阵乘的 K 方向先写 offset_k = tl.where(offset_k &lt; K, offset_k, 0)，随后算 mask_a = (offset_m\[:, None\] &lt; M) &amp; (offset_k\[None, :\] &lt; K)。失败的形状全是 K 不是 block_k 整数倍的；M = N = K = 1、a = 2、b = 3、block_k = 16 时输出 96。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -195,7 +196,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课练习首版：M = 70、块 32，最后一个 tile 负责第 64–95 行；测试在输出四周放了哨兵保护区，partial-m、partial-n 两项都通过。</t>
+          <t xml:space="preserve">M = 70、块 32，最后一个 tile 负责第 64–95 行；测试在输出四周放了哨兵保护区，partial-m、partial-n 两项都通过。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -225,7 +226,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课练习：A 是 \[M, K\] 行主序，B 是 \[K, N\] 行主序，M、N、K 方向的下标都经过了 tl.where。只给 offset_m 和 offset_k 加了声明后，A 成了异步拷贝，B 仍是同步读入。</t>
+          <t xml:space="preserve">Triton 3.7.1：A 是 \[M, K\] 行主序，B 是 \[K, N\] 行主序，M、N、K 方向的下标都经过了 tl.where。只给 offset_m 和 offset_k 加了声明后，A 成了异步拷贝，B 仍是同步读入。</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -249,12 +250,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 flatten 把 tile 循环和 K 循环合成一层后，循环体里出现的两个 scf.if 包住的是什么代码。</t>
+          <t xml:space="preserve">说明 flatten 把 tile 循环和 K 循环合成一层后，循环体里出现的两个 scf.if 包住的是什么代码，并把它们与流水的预热、排空区分开。</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课练习：flatten 开时 B 退回同步读入，学习者推测原因与合并引入的 if 有关。</t>
+          <t xml:space="preserve">Triton 3.7.1：flatten 开时 B 退回同步读入，有人推测原因与合并引入的 if 有关。</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -270,20 +271,21 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：合并后只剩一个大循环，原先在 K 循环之外的两段只在“k 为 0”和“最后一轮”时执行，所以各包进一个 if。
+• [T#B#两组概念]：tile 的 prologue、epilogue 是每个 tile 自己的计算，合并前后都是每个 tile 一次；流水的预热、排空是流水为读入安排的“先发几轮”和“最后等在途拷贝完成”，合并前每个 tile 一次，合并后每个 CTA 一次。讲 num_stages 软件流水时，后者也常被叫作 prologue、epilogue。
 • [T#B#与 B 的关系]：在 prologue 的 if 里算出的值作为 if 的结果传出，带不出连续性声明，B 的读入因此退回同步。
-[T#B,!c47f17#边界]：tile 的 prologue、epilogue 与流水的预热、排空名字相近，是本课反复混淆的一组概念。</t>
+[T#B,!c47f17#边界]：区分两组同名概念只问一句：这段代码是这个 tile 自己的计算（算坐标、清零、写回），还是流水为读入安排的（预热、排空）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">flatten 开时，B 的列下标 offset_n 在 tile 开头计算，声明经 scf.if 丢失。判断修复时应该把什么挪进 K 循环。</t>
+          <t xml:space="preserve">判断 flatten 下修复 B 的连续性时，只把声明挪进 K 循环为什么无效，应该把什么挪进去。</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课练习：只把 offset_n 那一行 tl.max_contiguous 声明挪进 K 循环后，TTGIR 逐字不变，B 仍是同步读入。</t>
+          <t xml:space="preserve">Triton 3.7.1，B 按行主序 \[K, N\] 存放，flatten 开时 B 退回同步读入。做法：offset_n 的计算留在 tile 开头，只把它的 tl.max_contiguous 声明挪进 K 循环；结果 B 仍是同步读入。</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -312,7 +314,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课 M1：预测“持久版对逐 tile 版的比值随 K 增大而下降，因为省掉的是重复发射的开销”。RTX 5090 上 K = 128、512、2048 时，逐 tile / 持久（flatten 关）为 1.023、1.002、1.000，持久关 / 持久开为 1.184、1.035、0.987。</t>
+          <t xml:space="preserve">RTX 5090、Triton 3.7.1 上的受控测量：预测“持久版对逐 tile 版的比值随 K 增大而下降，因为省掉的是重复发射的开销”。K = 128、512、2048 时，逐 tile / 持久（flatten 关）为 1.023、1.002、1.000，持久关 / 持久开为 1.184、1.035、0.987。</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -336,54 +338,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">理解 Triton 编译器说下标张量“连续”时指的是什么。</t>
+          <t xml:space="preserve">比较主机侧描述符（TensorDescriptor.from_tensor）与设备侧描述符（tl.make_tensor_descriptor）在 autotune 下哪个更省事，以及各自的代价。</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 09 课结课前答疑：tl.where 实实在在地构建了一个新张量，编译器却认为它的取值连续度只有 1。</t>
+          <t xml:space="preserve">Triton 3.7.1：教程的 TMA 版持久化矩阵乘与 autotune 配置表一起使用。</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">编译器说的是取值连续：张量里存的数是不是 v, v+1, v+2, …，也就是作为下标时指向的地址是否相邻；不是张量自己的存储连续（PyTorch 的 is_contiguous）。tl.where 后的新张量存储没有问题，但边界 tile 里的值是 192, …, 207, 0, 0, …，不再一路加一。</t>
+          <t xml:space="preserve">设备侧更省事：在 kernel 内构造时块大小已是编译期常量；主机侧描述符创建时块形状还没定，要靠 pre_hook 在每组配置发射前改写。主机侧的好处是省掉设备侧的 tensormap.replace 指令和每个描述符 128 字节的全局暂存。</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">这里的连续性指的难道不是结果张量的连续性吗？既然where实实在在地构建一个新张量，那这个新张量总该是连续的呀？</t>
+          <t xml:space="preserve">当我们进行autotune时，就需要主机侧描述符化，比较方便。</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：取值连续度、组首整除度、恒定度都是对张量取值的描述，三个声明函数声明的也都是取值上的性质。
-• [T#B#指针]：指针张量的取值就是地址：取值连续即地址相邻，整除度即按字节的对齐。
-[T#B,!c47f17#边界]：张量怎样分到各线程的寄存器里，由编译器选定的布局决定，声明管不到。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">比较主机侧描述符（TensorDescriptor.from_tensor）与设备侧描述符（tl.make_tensor_descriptor）在 autotune 下哪个更省事，以及各自的代价。</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 09 课节点 4：教程的 TMA 版持久化矩阵乘与 autotune 配置表一起使用。</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">设备侧更省事：在 kernel 内构造时块大小已是编译期常量；主机侧描述符创建时块形状还没定，要靠 pre_hook 在每组配置发射前改写。主机侧的好处是省掉设备侧的 tensormap.replace 指令和每个描述符 128 字节的全局暂存。</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">当我们进行autotune时，就需要主机侧描述符化，比较方便。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：主机侧描述符的块形状写在描述符对象里，autotune 每换一组块大小都要改写一次，所以需要钩子。
 • [T#B#设备侧适合]：发射时还不确定的张量，例如 grouped GEMM 每个问题各自的矩阵，只能在设备侧构造。
@@ -391,90 +364,32 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">解释同一 num_stages 下，sm_90 的矩阵乘为什么比 sm_120 多用共享内存、少用寄存器。</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 09 课综合验收：寄存器减少与共享内存增加是不是同一件事的两面。</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">两种目标的提前量相同，都是 num_stages − 1 轮；sm_90 的操作数留在共享内存里被 wgmma 就地读、槽占得更久，sm_120 的操作数要取进寄存器，所以一个槽多、一个寄存器多。</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">共享内存不断增加，是为了增加缓冲槽位空间，让尽可能多的数据提前开始搬，提前准备好。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：共享内存变多不是为了提前更多，而是操作数换了地方住：从线程的寄存器挪到了共享内存。
-• [T#B#提前量]：提前多少轮只由 num_stages 决定，两代相同。
-[T#B,!c47f17#边界]：这一点在节点 4 已经答对，综合题里又回退成了“提前更多”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">判断一个 kernel 版本多用了共享内存、少用了寄存器，能否据此解释它变慢了。</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 09 课 M1：K = 2048 时持久版开 flatten 比不开慢约 1.3%；开 flatten 的版本共享内存 73,728 字节、每线程 154 个寄存器，不开的是 65,536 字节、182 个；三个版本每个 SM 都只驻留 1 个 CTA。</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">资源用量只有在改变每个 SM 能驻留的 CTA 数时才影响速度；这里三个版本都只驻留 1 个 CTA，多出的共享内存和少用的寄存器都不是变慢的原因。</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K=2048时，比值低于1，flatten反而有负收益。这可能是因为共享内存用的更多？</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先算驻留数：每个 SM 放不下两个 CTA 时，单个 CTA 多用一点资源并不改变并行度。
-• [T#B#本例]：两个 CTA 需要 131,072 字节以上的共享内存，或 2 × 154 × 256 = 78,848 个寄存器，超过每个 SM 的 65,536 个，都放不下。
-[T#B,!c47f17#边界]：flatten 在大 K 下代价的真正来源没有验证，一个可能是合并后每轮都要做的判断。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">把持久化矩阵乘移植到别的后端时，判断怎样从编译产物确认持久化本身已经实现。</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">第 09 课综合验收：把持久版迁到没有 cp.async 与 TMA 的非 NVIDIA 后端，先验证什么。</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">持久化是手写代码与包装函数决定的，不是编译器的变换：在 TTGIR 里表现为一层步长是常数（NUM_SMS）的 scf.for tile 循环，网格由包装函数取 min(SM 数, tile 数)。</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">要把 Triton 3.7.1 的持久版矩阵乘迁到没有 cp.async 与 TMA 的非 NVIDIA 后端，动手之前先看编译产物。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">持久化是手写代码与包装函数决定的，不是编译器的变换：包装函数把网格设为 min(SM 数, tile 数)，kernel 里手写一层以 NUM_SMS 为步长领取 tile 的循环；编译器只是照着编出这层循环。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">对于非nv加速器，我会先看编译产物中发射动作是不是从tile循环中提出来了</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：发射几次由主机决定，编译产物里不会出现“把发射提出循环”这种变换。
-• [T#B#要验证的]：会受硬件差异影响的是 flatten 的收益：先看有没有异步拷贝，再看循环里是否提前读取下一个 tile 的数据。
-[T#B,!c47f17#边界]：复查时学习者答对：持久化在 TTGIR 里表现为 tile 循环。</t>
+• [T#B#产物里]：Triton 3.7.1 中，flatten 关时 TTGIR 里是一层步长为常数（NUM_SMS）的 scf.for tile 循环；flatten 开时它和 K 循环已合成一个 scf.for，tile 编号在“进入新 tile”的 scf.if 里前进。循环合并在生成 TTGIR 时才做，TTIR 里仍能看到原来的 tile 循环。
+[T#B,!c47f17#边界]：网格是持久化的另一半证据：只看 kernel 的编译产物，看不出发射了多少个 CTA，要看包装函数。</t>
         </is>
       </c>
     </row>
